--- a/documents/tableau_de_synthèse.xlsx
+++ b/documents/tableau_de_synthèse.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acnor\OneDrive\Bureau\Objectif Mr Robot\Travaux\Portfolio - le retour\documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acnor\OneDrive\Bureau\Stark\Travaux\Portfolio\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9763BF5B-1827-4862-A51F-B0BCB92059A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F366F60-0E11-4DDC-83BA-94F74116E15F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5475" yWindow="2895" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tableau de synthèse Épreuve E5" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E5'!$A$1:$H$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E5'!$A$1:$H$27</definedName>
   </definedNames>
   <calcPr calcId="181029" concurrentCalc="0"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="50">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -109,24 +109,12 @@
 </t>
   </si>
   <si>
-    <t>Réalisations en milieu professionnel en cours de première année</t>
-  </si>
-  <si>
-    <t>Réalisations en milieu professionnel en cours de seconde année</t>
-  </si>
-  <si>
     <t>SESSION 2026</t>
   </si>
   <si>
     <t>Installation et configuration d'un serveur Linux virtualisé avec la gestion des incidents GLPI</t>
   </si>
   <si>
-    <t xml:space="preserve">Refonte d'un jeu d'echec en langage C </t>
-  </si>
-  <si>
-    <t>Conception et développement du site internet immoblier Neige&amp;Soleil avec Html/CSS et PHP/Mysql</t>
-  </si>
-  <si>
     <t>Novembre 2025</t>
   </si>
   <si>
@@ -136,9 +124,6 @@
     <t>Octobre 2025</t>
   </si>
   <si>
-    <t>Conception et développement du site internet de l'école IRIS Paris en Html/CSS et PHP/Mysql</t>
-  </si>
-  <si>
     <t>Développement du site marchand d'appareils électroniques avec Shopify en mode projet</t>
   </si>
   <si>
@@ -154,9 +139,6 @@
     <t>NOM et prénom : BENNACEUR Rayan</t>
   </si>
   <si>
-    <t>Centre de formation : IRIS Paris</t>
-  </si>
-  <si>
     <t xml:space="preserve">Adresse URL du portfolio : </t>
   </si>
   <si>
@@ -166,7 +148,55 @@
     <t>Elaboration d'une veille technologique sur le hacking</t>
   </si>
   <si>
-    <t>Conception et développement du site internet E-Ensiegnement avec WordPresse</t>
+    <t>Janvier 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Refonte d'un jeu de bataille navale en langage C </t>
+  </si>
+  <si>
+    <t>Conception et développement du site internet de l'école IRIS Paris en Html/CSS, PHP et SQL</t>
+  </si>
+  <si>
+    <t>Conception et développement du site internet immoblier Neige&amp;Soleil avec Html/CSS, PHP et SQL</t>
+  </si>
+  <si>
+    <t>Développement d’un site de vente et de gestion d’appareils électroniques en Html/CSS, PHP et SQL</t>
+  </si>
+  <si>
+    <t>Juillet 2025</t>
+  </si>
+  <si>
+    <t>Elaboration d'une veille technologique sur le Green computing</t>
+  </si>
+  <si>
+    <t>Février - Mars 2026</t>
+  </si>
+  <si>
+    <t>Mars - Avril 2026</t>
+  </si>
+  <si>
+    <t>Conception et développement d'un site internet E-Learning avec WordPress</t>
+  </si>
+  <si>
+    <t>Épreuve E6 - Conception d'une application lourde de gestion d'une auto-école en Java et SQL</t>
+  </si>
+  <si>
+    <t>Octobre - Décembre 2025</t>
+  </si>
+  <si>
+    <t>Réalisations en milieu professionnel en cours de la première année</t>
+  </si>
+  <si>
+    <t>Réalisations en milieu professionnel en cours de la seconde année</t>
+  </si>
+  <si>
+    <t>Épreuve E6 - Conception et développement d'un site web de gestion d'une auto-école Html/CSS, PHP et SQL</t>
+  </si>
+  <si>
+    <t>Centre de formation : IRIS Paris -  6-8 Impasse des 2 Cousins, Paris 75017</t>
+  </si>
+  <si>
+    <t>Conception et déploiement d'un Portfolio en HTML/CSS et Javascript</t>
   </si>
 </sst>
 </file>
@@ -253,7 +283,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="32">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -391,43 +421,6 @@
         <color theme="2" tint="-0.749992370372631"/>
       </top>
       <bottom style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </top>
-      <bottom style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </top>
-      <bottom style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </right>
-      <top style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </top>
-      <bottom style="thin">
         <color theme="2" tint="-0.749992370372631"/>
       </bottom>
       <diagonal/>
@@ -614,53 +607,57 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </left>
+      <left/>
       <right/>
-      <top style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </top>
-      <bottom/>
+      <top/>
+      <bottom style="medium">
+        <color theme="2" tint="-0.749992370372631"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="medium">
+        <color theme="2" tint="-0.749992370372631"/>
+      </left>
       <right/>
-      <top style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </right>
-      <top style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </top>
-      <bottom/>
+      <top/>
+      <bottom style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
+      <bottom style="thin">
         <color theme="2" tint="-0.749992370372631"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
+      <right style="thin">
+        <color indexed="64"/>
       </right>
       <top/>
       <bottom style="medium">
         <color theme="2" tint="-0.749992370372631"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF494529"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF494529"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF494529"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF494529"/>
       </bottom>
       <diagonal/>
     </border>
@@ -669,7 +666,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -722,41 +719,62 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -764,67 +782,40 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1135,67 +1126,68 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AQ81"/>
+  <dimension ref="A1:AQ82"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="70.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="24.5703125" style="1" customWidth="1"/>
-    <col min="3" max="8" width="18.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="31.7109375" style="1" customWidth="1"/>
+    <col min="3" max="5" width="19.85546875" style="1" customWidth="1"/>
+    <col min="6" max="8" width="20" style="1" customWidth="1"/>
     <col min="9" max="43" width="11.42578125" customWidth="1"/>
     <col min="44" max="16384" width="10.85546875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="H1" s="32"/>
-    </row>
-    <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="32" t="s">
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" s="31"/>
+    </row>
+    <row r="2" spans="1:43" ht="41.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
     </row>
     <row r="3" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="45" t="s">
-        <v>34</v>
-      </c>
-      <c r="B3" s="46"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="50" t="s">
-        <v>37</v>
-      </c>
-      <c r="G3" s="51"/>
-      <c r="H3" s="52"/>
+      <c r="A3" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="36"/>
+      <c r="H3" s="36"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="48" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4" s="49"/>
-      <c r="C4" s="49"/>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
+      <c r="A4" s="34" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" s="35"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
       <c r="F4" s="27" t="s">
         <v>2</v>
       </c>
@@ -1207,22 +1199,22 @@
       </c>
     </row>
     <row r="5" spans="1:43" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="41" t="s">
-        <v>36</v>
-      </c>
-      <c r="B5" s="42"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="42"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="43"/>
-      <c r="H5" s="44"/>
+      <c r="A5" s="47" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="48"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="50"/>
     </row>
     <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="30" t="s">
+      <c r="A6" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="39" t="s">
+      <c r="B6" s="45" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -1245,8 +1237,8 @@
       </c>
     </row>
     <row r="7" spans="1:43" s="2" customFormat="1" ht="324.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="31"/>
-      <c r="B7" s="40"/>
+      <c r="A7" s="38"/>
+      <c r="B7" s="46"/>
       <c r="C7" s="10" t="s">
         <v>13</v>
       </c>
@@ -1302,16 +1294,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A8" s="33" t="s">
+      <c r="A8" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="34"/>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34"/>
-      <c r="E8" s="34"/>
-      <c r="F8" s="34"/>
-      <c r="G8" s="34"/>
-      <c r="H8" s="35"/>
+      <c r="B8" s="40"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="41"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1350,10 +1342,10 @@
     </row>
     <row r="9" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="12" t="s">
         <v>23</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>27</v>
       </c>
       <c r="C9" s="16"/>
       <c r="D9" s="17"/>
@@ -1399,10 +1391,10 @@
     </row>
     <row r="10" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="18" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C10" s="17"/>
       <c r="D10" s="9"/>
@@ -1448,10 +1440,10 @@
     </row>
     <row r="11" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="14" t="s">
         <v>24</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>28</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
@@ -1497,10 +1489,10 @@
     </row>
     <row r="12" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="18" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
@@ -1546,10 +1538,10 @@
     </row>
     <row r="13" spans="1:43" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="18" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C13" s="17"/>
       <c r="D13" s="9"/>
@@ -1595,10 +1587,10 @@
     </row>
     <row r="14" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="18" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
@@ -1644,15 +1636,15 @@
     </row>
     <row r="15" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="18" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="17"/>
-      <c r="F15" s="9"/>
+      <c r="F15" s="17"/>
       <c r="G15" s="9"/>
       <c r="H15" s="19"/>
       <c r="I15"/>
@@ -1692,14 +1684,18 @@
       <c r="AQ15"/>
     </row>
     <row r="16" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="18"/>
-      <c r="B16" s="15"/>
+      <c r="A16" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>44</v>
+      </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
+      <c r="E16" s="17"/>
       <c r="F16" s="9"/>
       <c r="G16" s="9"/>
-      <c r="H16" s="19"/>
+      <c r="H16" s="20"/>
       <c r="I16"/>
       <c r="J16"/>
       <c r="K16"/>
@@ -1737,14 +1733,18 @@
       <c r="AQ16"/>
     </row>
     <row r="17" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="18"/>
-      <c r="B17" s="15"/>
+      <c r="A17" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>33</v>
+      </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
       <c r="G17" s="9"/>
-      <c r="H17" s="19"/>
+      <c r="H17" s="20"/>
       <c r="I17"/>
       <c r="J17"/>
       <c r="K17"/>
@@ -1782,13 +1782,17 @@
       <c r="AQ17"/>
     </row>
     <row r="18" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="18"/>
-      <c r="B18" s="15"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
+      <c r="A18" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="17"/>
       <c r="H18" s="19"/>
       <c r="I18"/>
       <c r="J18"/>
@@ -1826,17 +1830,19 @@
       <c r="AP18"/>
       <c r="AQ18"/>
     </row>
-    <row r="19" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A19" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" s="37"/>
-      <c r="C19" s="37"/>
-      <c r="D19" s="37"/>
-      <c r="E19" s="37"/>
-      <c r="F19" s="37"/>
-      <c r="G19" s="37"/>
-      <c r="H19" s="38"/>
+    <row r="19" spans="1:43" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="19"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -1873,15 +1879,17 @@
       <c r="AP19"/>
       <c r="AQ19"/>
     </row>
-    <row r="20" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="18"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="19"/>
+    <row r="20" spans="1:43" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" s="43"/>
+      <c r="C20" s="43"/>
+      <c r="D20" s="43"/>
+      <c r="E20" s="43"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="43"/>
+      <c r="H20" s="44"/>
       <c r="I20"/>
       <c r="J20"/>
       <c r="K20"/>
@@ -1919,13 +1927,17 @@
       <c r="AQ20"/>
     </row>
     <row r="21" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="18"/>
-      <c r="B21" s="8"/>
+      <c r="A21" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>38</v>
+      </c>
       <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
       <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
+      <c r="G21" s="17"/>
       <c r="H21" s="19"/>
       <c r="I21"/>
       <c r="J21"/>
@@ -1964,16 +1976,14 @@
       <c r="AQ21"/>
     </row>
     <row r="22" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="36" t="s">
-        <v>21</v>
-      </c>
-      <c r="B22" s="37"/>
-      <c r="C22" s="37"/>
-      <c r="D22" s="37"/>
-      <c r="E22" s="37"/>
-      <c r="F22" s="37"/>
-      <c r="G22" s="37"/>
-      <c r="H22" s="38"/>
+      <c r="A22" s="18"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="19"/>
       <c r="I22"/>
       <c r="J22"/>
       <c r="K22"/>
@@ -2010,19 +2020,17 @@
       <c r="AP22"/>
       <c r="AQ22"/>
     </row>
-    <row r="23" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="B23" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="C23" s="17"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="19"/>
+    <row r="23" spans="1:43" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="42" t="s">
+        <v>46</v>
+      </c>
+      <c r="B23" s="43"/>
+      <c r="C23" s="43"/>
+      <c r="D23" s="43"/>
+      <c r="E23" s="43"/>
+      <c r="F23" s="43"/>
+      <c r="G23" s="43"/>
+      <c r="H23" s="44"/>
       <c r="I23"/>
       <c r="J23"/>
       <c r="K23"/>
@@ -2059,19 +2067,19 @@
       <c r="AP23"/>
       <c r="AQ23"/>
     </row>
-    <row r="24" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="22" t="s">
-        <v>32</v>
-      </c>
-      <c r="B24" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="C24" s="24"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="24"/>
-      <c r="F24" s="24"/>
-      <c r="G24" s="25"/>
-      <c r="H24" s="26"/>
+    <row r="24" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" s="17"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="19"/>
       <c r="I24"/>
       <c r="J24"/>
       <c r="K24"/>
@@ -2108,15 +2116,19 @@
       <c r="AP24"/>
       <c r="AQ24"/>
     </row>
-    <row r="25" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25"/>
-      <c r="B25"/>
-      <c r="C25"/>
-      <c r="D25"/>
-      <c r="E25"/>
-      <c r="F25"/>
-      <c r="G25"/>
-      <c r="H25"/>
+    <row r="25" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="B25" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25" s="24"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="25"/>
+      <c r="H25" s="26"/>
       <c r="I25"/>
       <c r="J25"/>
       <c r="K25"/>
@@ -2154,14 +2166,14 @@
       <c r="AQ25"/>
     </row>
     <row r="26" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="5"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
+      <c r="A26"/>
+      <c r="B26"/>
+      <c r="C26"/>
+      <c r="D26"/>
+      <c r="E26"/>
+      <c r="F26"/>
+      <c r="G26"/>
+      <c r="H26"/>
       <c r="I26"/>
       <c r="J26"/>
       <c r="K26"/>
@@ -2198,15 +2210,15 @@
       <c r="AP26"/>
       <c r="AQ26"/>
     </row>
-    <row r="27" spans="1:43" s="2" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27"/>
-      <c r="B27"/>
-      <c r="C27"/>
-      <c r="D27"/>
-      <c r="E27"/>
-      <c r="F27"/>
-      <c r="G27"/>
-      <c r="H27"/>
+    <row r="27" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="5"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2243,7 +2255,7 @@
       <c r="AP27"/>
       <c r="AQ27"/>
     </row>
-    <row r="28" spans="1:43" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:43" s="2" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28"/>
       <c r="B28"/>
       <c r="C28"/>
@@ -2288,7 +2300,7 @@
       <c r="AP28"/>
       <c r="AQ28"/>
     </row>
-    <row r="29" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:43" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29"/>
       <c r="B29"/>
       <c r="C29"/>
@@ -2369,6 +2381,14 @@
       <c r="AG30"/>
       <c r="AH30"/>
       <c r="AI30"/>
+      <c r="AJ30"/>
+      <c r="AK30"/>
+      <c r="AL30"/>
+      <c r="AM30"/>
+      <c r="AN30"/>
+      <c r="AO30"/>
+      <c r="AP30"/>
+      <c r="AQ30"/>
     </row>
     <row r="31" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31"/>
@@ -2406,14 +2426,6 @@
       <c r="AG31"/>
       <c r="AH31"/>
       <c r="AI31"/>
-      <c r="AJ31"/>
-      <c r="AK31"/>
-      <c r="AL31"/>
-      <c r="AM31"/>
-      <c r="AN31"/>
-      <c r="AO31"/>
-      <c r="AP31"/>
-      <c r="AQ31"/>
     </row>
     <row r="32" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32"/>
@@ -2550,7 +2562,7 @@
       <c r="AP34"/>
       <c r="AQ34"/>
     </row>
-    <row r="35" spans="1:43" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35"/>
       <c r="B35"/>
       <c r="C35"/>
@@ -2595,7 +2607,51 @@
       <c r="AP35"/>
       <c r="AQ35"/>
     </row>
-    <row r="36" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="36" spans="1:43" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A36"/>
+      <c r="B36"/>
+      <c r="C36"/>
+      <c r="D36"/>
+      <c r="E36"/>
+      <c r="F36"/>
+      <c r="G36"/>
+      <c r="H36"/>
+      <c r="I36"/>
+      <c r="J36"/>
+      <c r="K36"/>
+      <c r="L36"/>
+      <c r="M36"/>
+      <c r="N36"/>
+      <c r="O36"/>
+      <c r="P36"/>
+      <c r="Q36"/>
+      <c r="R36"/>
+      <c r="S36"/>
+      <c r="T36"/>
+      <c r="U36"/>
+      <c r="V36"/>
+      <c r="W36"/>
+      <c r="X36"/>
+      <c r="Y36"/>
+      <c r="Z36"/>
+      <c r="AA36"/>
+      <c r="AB36"/>
+      <c r="AC36"/>
+      <c r="AD36"/>
+      <c r="AE36"/>
+      <c r="AF36"/>
+      <c r="AG36"/>
+      <c r="AH36"/>
+      <c r="AI36"/>
+      <c r="AJ36"/>
+      <c r="AK36"/>
+      <c r="AL36"/>
+      <c r="AM36"/>
+      <c r="AN36"/>
+      <c r="AO36"/>
+      <c r="AP36"/>
+      <c r="AQ36"/>
+    </row>
     <row r="37" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="38" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="39" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -2632,16 +2688,7 @@
     <row r="70" spans="1:8" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="71" spans="1:8" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="72" spans="1:8" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="73" spans="1:8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="1"/>
-      <c r="B73" s="1"/>
-      <c r="C73" s="1"/>
-      <c r="D73" s="1"/>
-      <c r="E73" s="1"/>
-      <c r="F73" s="1"/>
-      <c r="G73" s="1"/>
-      <c r="H73" s="1"/>
-    </row>
+    <row r="73" spans="1:8" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="74" spans="1:8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
@@ -2722,39 +2769,40 @@
       <c r="G81" s="1"/>
       <c r="H81" s="1"/>
     </row>
+    <row r="82" spans="1:8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="1"/>
+      <c r="B82" s="1"/>
+      <c r="C82" s="1"/>
+      <c r="D82" s="1"/>
+      <c r="E82" s="1"/>
+      <c r="F82" s="1"/>
+      <c r="G82" s="1"/>
+      <c r="H82" s="1"/>
+    </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="A5:H5"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="F3:H3"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A22:H22"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="A5:H5"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="49" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="46" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="191d0fcf-6d89-4c90-807a-10f37b8d7a4c">
@@ -2763,6 +2811,15 @@
     <TaxCatchAll xmlns="9a7dc87b-2be1-4fee-871a-355a79ca984c" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2961,14 +3018,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{240DE218-FED0-48EE-B696-C7623217CB73}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A3CCF3B-7B88-440F-8A0A-FBED7FBF06E5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -2981,6 +3030,14 @@
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="191d0fcf-6d89-4c90-807a-10f37b8d7a4c"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{240DE218-FED0-48EE-B696-C7623217CB73}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/documents/tableau_de_synthèse.xlsx
+++ b/documents/tableau_de_synthèse.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acnor\OneDrive\Bureau\Stark\Travaux\Portfolio\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F366F60-0E11-4DDC-83BA-94F74116E15F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5427AD5-2EBE-4C43-BC55-821651A13549}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5475" yWindow="2895" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -139,9 +139,6 @@
     <t>NOM et prénom : BENNACEUR Rayan</t>
   </si>
   <si>
-    <t xml:space="preserve">Adresse URL du portfolio : </t>
-  </si>
-  <si>
     <t>N° candidat : 02544748433</t>
   </si>
   <si>
@@ -160,9 +157,6 @@
     <t>Conception et développement du site internet immoblier Neige&amp;Soleil avec Html/CSS, PHP et SQL</t>
   </si>
   <si>
-    <t>Développement d’un site de vente et de gestion d’appareils électroniques en Html/CSS, PHP et SQL</t>
-  </si>
-  <si>
     <t>Juillet 2025</t>
   </si>
   <si>
@@ -197,6 +191,12 @@
   </si>
   <si>
     <t>Conception et déploiement d'un Portfolio en HTML/CSS et Javascript</t>
+  </si>
+  <si>
+    <t>Adresse URL du portfolio : https://killbill-jpg.github.io/Portfolio/</t>
+  </si>
+  <si>
+    <t>Développement d’un site de gestion d'inventaire d’appareils électroniques en Html/CSS, PHP et SQL</t>
   </si>
 </sst>
 </file>
@@ -269,7 +269,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -279,6 +279,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -666,7 +672,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -757,6 +763,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1138,56 +1147,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31" t="s">
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="31"/>
+      <c r="H1" s="32"/>
     </row>
     <row r="2" spans="1:43" ht="41.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
     </row>
     <row r="3" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="33"/>
-      <c r="C3" s="33"/>
-      <c r="D3" s="33"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="G3" s="36"/>
-      <c r="H3" s="36"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="37"/>
+      <c r="H3" s="37"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="B4" s="35"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
+      <c r="A4" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
       <c r="F4" s="27" t="s">
         <v>2</v>
       </c>
@@ -1199,22 +1208,22 @@
       </c>
     </row>
     <row r="5" spans="1:43" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="47" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="50"/>
+      <c r="A5" s="48" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="50"/>
+      <c r="G5" s="50"/>
+      <c r="H5" s="51"/>
     </row>
     <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="37" t="s">
+      <c r="A6" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="45" t="s">
+      <c r="B6" s="46" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -1237,8 +1246,8 @@
       </c>
     </row>
     <row r="7" spans="1:43" s="2" customFormat="1" ht="324.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="38"/>
-      <c r="B7" s="46"/>
+      <c r="A7" s="39"/>
+      <c r="B7" s="47"/>
       <c r="C7" s="10" t="s">
         <v>13</v>
       </c>
@@ -1294,16 +1303,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A8" s="39" t="s">
+      <c r="A8" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="40"/>
-      <c r="C8" s="40"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="40"/>
-      <c r="F8" s="40"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="41"/>
+      <c r="B8" s="41"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="42"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1391,7 +1400,7 @@
     </row>
     <row r="10" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="18" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B10" s="13" t="s">
         <v>23</v>
@@ -1440,7 +1449,7 @@
     </row>
     <row r="11" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>24</v>
@@ -1489,7 +1498,7 @@
     </row>
     <row r="12" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>24</v>
@@ -1587,7 +1596,7 @@
     </row>
     <row r="14" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B14" s="15" t="s">
         <v>22</v>
@@ -1636,7 +1645,7 @@
     </row>
     <row r="15" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B15" s="15" t="s">
         <v>22</v>
@@ -1685,10 +1694,10 @@
     </row>
     <row r="16" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="18" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
@@ -1734,10 +1743,10 @@
     </row>
     <row r="17" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="18" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
@@ -1783,10 +1792,10 @@
     </row>
     <row r="18" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="30" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C18" s="17"/>
       <c r="D18" s="17"/>
@@ -1832,10 +1841,10 @@
     </row>
     <row r="19" spans="1:43" s="2" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="18" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C19" s="17"/>
       <c r="D19" s="17"/>
@@ -1880,16 +1889,16 @@
       <c r="AQ19"/>
     </row>
     <row r="20" spans="1:43" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="42" t="s">
-        <v>45</v>
-      </c>
-      <c r="B20" s="43"/>
-      <c r="C20" s="43"/>
-      <c r="D20" s="43"/>
-      <c r="E20" s="43"/>
-      <c r="F20" s="43"/>
-      <c r="G20" s="43"/>
-      <c r="H20" s="44"/>
+      <c r="A20" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="44"/>
+      <c r="C20" s="44"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="44"/>
+      <c r="H20" s="45"/>
       <c r="I20"/>
       <c r="J20"/>
       <c r="K20"/>
@@ -1928,14 +1937,14 @@
     </row>
     <row r="21" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="18" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
+      <c r="E21" s="31"/>
       <c r="F21" s="9"/>
       <c r="G21" s="17"/>
       <c r="H21" s="19"/>
@@ -2021,16 +2030,16 @@
       <c r="AQ22"/>
     </row>
     <row r="23" spans="1:43" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="42" t="s">
-        <v>46</v>
-      </c>
-      <c r="B23" s="43"/>
-      <c r="C23" s="43"/>
-      <c r="D23" s="43"/>
-      <c r="E23" s="43"/>
-      <c r="F23" s="43"/>
-      <c r="G23" s="43"/>
-      <c r="H23" s="44"/>
+      <c r="A23" s="43" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="44"/>
+      <c r="C23" s="44"/>
+      <c r="D23" s="44"/>
+      <c r="E23" s="44"/>
+      <c r="F23" s="44"/>
+      <c r="G23" s="44"/>
+      <c r="H23" s="45"/>
       <c r="I23"/>
       <c r="J23"/>
       <c r="K23"/>
@@ -3020,15 +3029,15 @@
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A3CCF3B-7B88-440F-8A0A-FBED7FBF06E5}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="9a7dc87b-2be1-4fee-871a-355a79ca984c"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="9a7dc87b-2be1-4fee-871a-355a79ca984c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="191d0fcf-6d89-4c90-807a-10f37b8d7a4c"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
